--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -48,10 +48,6 @@
   </si>
   <si>
     <t>单据类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.typeName}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -147,6 +143,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -216,6 +213,10 @@
   </si>
   <si>
     <t>{.requireDate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.orderTypeName}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -235,12 +236,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -597,52 +600,52 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>1</v>
@@ -659,55 +662,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>2</v>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>{.code}</t>
   </si>
@@ -164,10 +164,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>可出数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>已出库数量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -189,10 +185,6 @@
   </si>
   <si>
     <t>{.scarceQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.availableQty}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -578,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -588,11 +580,11 @@
     <col min="5" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="9" width="20.125" customWidth="1"/>
     <col min="10" max="10" width="22.5" customWidth="1"/>
-    <col min="11" max="18" width="20.125" customWidth="1"/>
-    <col min="19" max="21" width="20.625" customWidth="1"/>
+    <col min="11" max="17" width="20.125" customWidth="1"/>
+    <col min="18" max="20" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -644,25 +636,22 @@
       <c r="Q1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>33</v>
+      <c r="R1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
@@ -692,37 +681,34 @@
         <v>26</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>40</v>
+      <c r="R2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="C3" s="2"/>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,92 +14,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>{.code}</t>
-  </si>
-  <si>
-    <t>最新审核人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.approveUserName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.createTime}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>销售单号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>单据类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>单据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.approveStatusName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>作废状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.invalidStatusName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>客户</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.customerName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>销售组织</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售部门</t>
   </si>
   <si>
     <t>销售员</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.salesOrgName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.sellerName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>发货状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.deliveryStatusName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>s</t>
     </r>
     <r>
@@ -107,24 +58,102 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>ku</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售单价</t>
+  </si>
+  <si>
+    <t>销售数量</t>
+  </si>
+  <si>
+    <t>价税合计</t>
+  </si>
+  <si>
+    <t>采购单价</t>
+  </si>
+  <si>
+    <t>缺货数量</t>
+  </si>
+  <si>
+    <t>已出库数量</t>
+  </si>
+  <si>
+    <t>剩余未出数量</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>销售金额</t>
+  </si>
+  <si>
+    <t>销售总成本</t>
+  </si>
+  <si>
+    <t>销售毛利</t>
+  </si>
+  <si>
+    <t>销售毛利率</t>
+  </si>
+  <si>
+    <t>要货日期</t>
+  </si>
+  <si>
+    <t>最新审核人</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.orderTypeName}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.customerName}</t>
+  </si>
+  <si>
+    <t>{.salesOrgName}</t>
+  </si>
+  <si>
+    <t>{.salesDeptName}</t>
+  </si>
+  <si>
+    <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.deliveryStatusName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.</t>
     </r>
     <r>
@@ -132,7 +161,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -143,80 +171,72 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.price}</t>
   </si>
   <si>
     <t>{.qty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缺货数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>已出库数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>剩余未出数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售金额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>要货日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxAmount}</t>
+  </si>
+  <si>
+    <t>{.purchasePrice}</t>
   </si>
   <si>
     <t>{.scarceQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.deliveryQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.waitQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.unit}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.amount}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.saleCost}</t>
+  </si>
+  <si>
+    <t>{.saleProfit}</t>
+  </si>
+  <si>
+    <t>{.saleProfitRate}</t>
   </si>
   <si>
     <t>{.requireDate}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.orderTypeName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -228,35 +248,356 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -279,13 +620,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -295,14 +878,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -564,156 +1191,198 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="25.625" customWidth="1"/>
     <col min="3" max="3" width="20.625" customWidth="1"/>
     <col min="4" max="4" width="22.375" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="9" width="20.125" customWidth="1"/>
-    <col min="10" max="10" width="22.5" customWidth="1"/>
-    <col min="11" max="17" width="20.125" customWidth="1"/>
-    <col min="18" max="20" width="20.625" customWidth="1"/>
+    <col min="6" max="10" width="20.125" customWidth="1"/>
+    <col min="11" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="24" width="20.125" customWidth="1"/>
+    <col min="25" max="27" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>5</v>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="3" spans="3:3">
       <c r="C3" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -34,10 +34,10 @@
     <t>销售组织</t>
   </si>
   <si>
+    <t>销售员</t>
+  </si>
+  <si>
     <t>销售部门</t>
-  </si>
-  <si>
-    <t>销售员</t>
   </si>
   <si>
     <t>发货状态</t>
@@ -68,40 +68,40 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>销售数量</t>
+  </si>
+  <si>
+    <t>缺货数量</t>
+  </si>
+  <si>
+    <t>已出库数量</t>
+  </si>
+  <si>
+    <t>剩余未出数量</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>销售金额</t>
+  </si>
+  <si>
     <t>销售单价</t>
   </si>
   <si>
-    <t>销售数量</t>
-  </si>
-  <si>
     <t>价税合计</t>
   </si>
   <si>
     <t>采购单价</t>
   </si>
   <si>
-    <t>缺货数量</t>
-  </si>
-  <si>
-    <t>已出库数量</t>
-  </si>
-  <si>
-    <t>剩余未出数量</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>销售金额</t>
-  </si>
-  <si>
     <t>销售总成本</t>
   </si>
   <si>
     <t>销售毛利</t>
   </si>
   <si>
-    <t>销售毛利率</t>
+    <t>销售毛利率（%）</t>
   </si>
   <si>
     <t>要货日期</t>
@@ -134,10 +134,10 @@
     <t>{.salesOrgName}</t>
   </si>
   <si>
+    <t>{.sellerName}</t>
+  </si>
+  <si>
     <t>{.salesDeptName}</t>
-  </si>
-  <si>
-    <t>{.sellerName}</t>
   </si>
   <si>
     <t>{.deliveryStatusName}</t>
@@ -178,31 +178,31 @@
     </r>
   </si>
   <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.scarceQty}</t>
+  </si>
+  <si>
+    <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.waitQty}</t>
+  </si>
+  <si>
+    <t>{.unit}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
     <t>{.price}</t>
   </si>
   <si>
-    <t>{.qty}</t>
-  </si>
-  <si>
     <t>{.taxAmount}</t>
   </si>
   <si>
     <t>{.purchasePrice}</t>
-  </si>
-  <si>
-    <t>{.scarceQty}</t>
-  </si>
-  <si>
-    <t>{.deliveryQty}</t>
-  </si>
-  <si>
-    <t>{.waitQty}</t>
-  </si>
-  <si>
-    <t>{.unit}</t>
-  </si>
-  <si>
-    <t>{.amount}</t>
   </si>
   <si>
     <t>{.saleCost}</t>
@@ -1206,8 +1206,10 @@
     <col min="4" max="4" width="22.375" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="10" width="20.125" customWidth="1"/>
-    <col min="11" max="12" width="22.5" customWidth="1"/>
-    <col min="13" max="24" width="20.125" customWidth="1"/>
+    <col min="11" max="11" width="22.5" customWidth="1"/>
+    <col min="12" max="17" width="20.125" customWidth="1"/>
+    <col min="18" max="18" width="22.5" customWidth="1"/>
+    <col min="19" max="24" width="20.125" customWidth="1"/>
     <col min="25" max="27" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>销售单号</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>要货日期</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>最新审核人</t>
@@ -215,6 +218,9 @@
   </si>
   <si>
     <t>{.requireDate}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1197,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1209,11 +1215,11 @@
     <col min="11" max="11" width="22.5" customWidth="1"/>
     <col min="12" max="17" width="20.125" customWidth="1"/>
     <col min="18" max="18" width="22.5" customWidth="1"/>
-    <col min="19" max="24" width="20.125" customWidth="1"/>
-    <col min="25" max="27" width="20.625" customWidth="1"/>
+    <col min="19" max="25" width="20.125" customWidth="1"/>
+    <col min="26" max="28" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,88 +1301,94 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="3:3">

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>销售单号</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
   <si>
     <t>最新审核人</t>
@@ -218,6 +221,9 @@
   </si>
   <si>
     <t>{.requireDate}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.detailRemark}</t>
@@ -1203,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1216,10 +1222,10 @@
     <col min="12" max="17" width="20.125" customWidth="1"/>
     <col min="18" max="18" width="22.5" customWidth="1"/>
     <col min="19" max="25" width="20.125" customWidth="1"/>
-    <col min="26" max="28" width="20.625" customWidth="1"/>
+    <col min="26" max="29" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1304,91 +1310,97 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="3:3">

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>销售单号</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>客户</t>
+  </si>
+  <si>
+    <t>国家</t>
   </si>
   <si>
     <t>销售组织</t>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t>{.customerName}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
   </si>
   <si>
     <t>{.salesOrgName}</t>
@@ -241,7 +247,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -271,55 +277,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -364,6 +334,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -409,7 +394,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -424,49 +430,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,121 +568,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,21 +635,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,6 +668,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,148 +741,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -893,52 +899,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1209,23 +1215,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="25.625" customWidth="1"/>
     <col min="3" max="3" width="20.625" customWidth="1"/>
     <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="10" width="20.125" customWidth="1"/>
-    <col min="11" max="11" width="22.5" customWidth="1"/>
-    <col min="12" max="17" width="20.125" customWidth="1"/>
-    <col min="18" max="18" width="22.5" customWidth="1"/>
-    <col min="19" max="25" width="20.125" customWidth="1"/>
-    <col min="26" max="29" width="20.625" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="11" width="20.125" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="18" width="20.125" customWidth="1"/>
+    <col min="19" max="19" width="22.5" customWidth="1"/>
+    <col min="20" max="26" width="20.125" customWidth="1"/>
+    <col min="27" max="30" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,94 +1319,100 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="3:3">

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -31,7 +31,7 @@
     <t>客户</t>
   </si>
   <si>
-    <t>国家</t>
+    <t>收货国家</t>
   </si>
   <si>
     <t>销售组织</t>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24225" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>销售单号</t>
   </si>
@@ -41,6 +41,24 @@
   </si>
   <si>
     <t>销售部门</t>
+  </si>
+  <si>
+    <t>银行手续费</t>
+  </si>
+  <si>
+    <t>运费金额</t>
+  </si>
+  <si>
+    <t>收款账号</t>
+  </si>
+  <si>
+    <t>收款方式</t>
+  </si>
+  <si>
+    <t>收款日期</t>
+  </si>
+  <si>
+    <t>收款金额</t>
   </si>
   <si>
     <t>发货状态</t>
@@ -95,6 +113,15 @@
     <t>价税合计</t>
   </si>
   <si>
+    <t>汇率</t>
+  </si>
+  <si>
+    <t>销售金额（本位币）</t>
+  </si>
+  <si>
+    <t>价税合计（本位币）</t>
+  </si>
+  <si>
     <t>采购单价</t>
   </si>
   <si>
@@ -107,6 +134,15 @@
     <t>销售毛利率（%）</t>
   </si>
   <si>
+    <t>贸易条款</t>
+  </si>
+  <si>
+    <t>报关费</t>
+  </si>
+  <si>
+    <t>结算币种</t>
+  </si>
+  <si>
     <t>要货日期</t>
   </si>
   <si>
@@ -150,6 +186,24 @@
   </si>
   <si>
     <t>{.salesDeptName}</t>
+  </si>
+  <si>
+    <t>{.bankServiceFee}</t>
+  </si>
+  <si>
+    <t>{.shippingFee}</t>
+  </si>
+  <si>
+    <t>{.receiveAccount}</t>
+  </si>
+  <si>
+    <t>{.receiveMethodName}</t>
+  </si>
+  <si>
+    <t>{.receiveDate}</t>
+  </si>
+  <si>
+    <t>{.receiveAmount}</t>
   </si>
   <si>
     <t>{.deliveryStatusName}</t>
@@ -214,6 +268,15 @@
     <t>{.taxAmount}</t>
   </si>
   <si>
+    <t>{.exchangeRate}</t>
+  </si>
+  <si>
+    <t>{.amountLocalCurrency}</t>
+  </si>
+  <si>
+    <t>{.allAmountLocalCurrency}</t>
+  </si>
+  <si>
     <t>{.purchasePrice}</t>
   </si>
   <si>
@@ -224,6 +287,15 @@
   </si>
   <si>
     <t>{.saleProfitRate}</t>
+  </si>
+  <si>
+    <t>{.tradeTermName}</t>
+  </si>
+  <si>
+    <t>{.customsFee}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
   </si>
   <si>
     <t>{.requireDate}</t>
@@ -247,7 +319,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -277,6 +349,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -290,6 +390,14 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -334,14 +442,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -349,7 +450,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,6 +458,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -365,57 +473,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,13 +502,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,24 +568,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -490,18 +616,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -514,36 +628,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -562,24 +652,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -593,12 +671,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,6 +707,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,21 +755,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -741,148 +813,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -899,52 +971,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1215,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1223,15 +1295,17 @@
     <col min="3" max="3" width="20.625" customWidth="1"/>
     <col min="4" max="4" width="22.375" customWidth="1"/>
     <col min="5" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="11" width="20.125" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="13" max="18" width="20.125" customWidth="1"/>
-    <col min="19" max="19" width="22.5" customWidth="1"/>
-    <col min="20" max="26" width="20.125" customWidth="1"/>
-    <col min="27" max="30" width="20.625" customWidth="1"/>
+    <col min="7" max="17" width="20.125" customWidth="1"/>
+    <col min="18" max="18" width="22.5" customWidth="1"/>
+    <col min="19" max="24" width="20.125" customWidth="1"/>
+    <col min="25" max="25" width="22.5" customWidth="1"/>
+    <col min="26" max="28" width="20.125" customWidth="1"/>
+    <col min="29" max="29" width="28.375" customWidth="1"/>
+    <col min="30" max="38" width="20.125" customWidth="1"/>
+    <col min="39" max="42" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,97 +1396,169 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:42">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="3:3">

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24225" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>销售单号</t>
   </si>
@@ -315,18 +315,44 @@
   <si>
     <t>{.createTime}</t>
   </si>
+  <si>
+    <t>销售单价(本位币)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.priceLc}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>税率(%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>含税单价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>含税单价本位币</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxPriceLc}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -342,352 +368,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -710,255 +405,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -968,58 +421,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1281,14 +690,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AT3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="25.625" customWidth="1"/>
@@ -1299,13 +708,14 @@
     <col min="18" max="18" width="22.5" customWidth="1"/>
     <col min="19" max="24" width="20.125" customWidth="1"/>
     <col min="25" max="25" width="22.5" customWidth="1"/>
-    <col min="26" max="28" width="20.125" customWidth="1"/>
-    <col min="29" max="29" width="28.375" customWidth="1"/>
-    <col min="30" max="38" width="20.125" customWidth="1"/>
-    <col min="39" max="42" width="20.625" customWidth="1"/>
+    <col min="26" max="29" width="22.5" style="3" customWidth="1"/>
+    <col min="30" max="32" width="20.125" customWidth="1"/>
+    <col min="33" max="33" width="28.375" customWidth="1"/>
+    <col min="34" max="42" width="20.125" customWidth="1"/>
+    <col min="43" max="46" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,58 +792,70 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1510,63 +932,75 @@
         <v>66</v>
       </c>
       <c r="Z2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.15">
       <c r="C3" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24225" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>销售单价</t>
+  </si>
+  <si>
+    <t>销售单价(本位币)</t>
+  </si>
+  <si>
+    <t>税率(%)</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>含税单价本位币</t>
   </si>
   <si>
     <t>价税合计</t>
@@ -265,6 +277,18 @@
     <t>{.price}</t>
   </si>
   <si>
+    <t>{.priceLc}</t>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.taxPriceLc}</t>
+  </si>
+  <si>
     <t>{.taxAmount}</t>
   </si>
   <si>
@@ -314,45 +338,19 @@
   </si>
   <si>
     <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>销售单价(本位币)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.priceLc}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>税率(%)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.taxRate}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>含税单价</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.taxPrice}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>含税单价本位币</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.taxPriceLc}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -368,21 +366,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -405,9 +734,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -415,20 +986,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -690,14 +1308,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AT3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="25.625" customWidth="1"/>
@@ -708,299 +1326,299 @@
     <col min="18" max="18" width="22.5" customWidth="1"/>
     <col min="19" max="24" width="20.125" customWidth="1"/>
     <col min="25" max="25" width="22.5" customWidth="1"/>
-    <col min="26" max="29" width="22.5" style="3" customWidth="1"/>
+    <col min="26" max="29" width="22.5" style="1" customWidth="1"/>
     <col min="30" max="32" width="20.125" customWidth="1"/>
     <col min="33" max="33" width="28.375" customWidth="1"/>
     <col min="34" max="42" width="20.125" customWidth="1"/>
     <col min="43" max="46" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:46">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AP2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>41</v>
+      <c r="AT2" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="C3" s="2"/>
+    <row r="3" spans="3:3">
+      <c r="C3" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>